--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753444629_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.008444969144207771</v>
       </c>
       <c r="C2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>33250103</v>
+        <v>4159049</v>
       </c>
       <c r="L2" t="n">
-        <v>12484769</v>
+        <v>1548864</v>
       </c>
       <c r="M2" t="n">
-        <v>2310450</v>
+        <v>290766</v>
       </c>
       <c r="N2" t="n">
-        <v>51005</v>
+        <v>6438</v>
       </c>
       <c r="O2" t="n">
-        <v>1384178</v>
+        <v>170772</v>
       </c>
       <c r="P2" t="n">
-        <v>25611</v>
+        <v>2748</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999213218688965</v>
+        <v>0.9999494552612305</v>
       </c>
       <c r="R2" t="n">
-        <v>0.7153207063674927</v>
+        <v>0.709680438041687</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5356883406639099</v>
+        <v>0.5387051105499268</v>
       </c>
       <c r="T2" t="n">
-        <v>0.402884304523468</v>
+        <v>0.4065139293670654</v>
       </c>
       <c r="U2" t="n">
-        <v>0.04535559564828873</v>
+        <v>0.04611549526453018</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4042473137378693</v>
+        <v>0.4068935513496399</v>
       </c>
       <c r="W2" t="n">
-        <v>0.45120769739151</v>
+        <v>0.4490929841995239</v>
       </c>
       <c r="X2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50503824</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="AG2" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AH2" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AI2" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AK2" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9562234282493591</v>
+        <v>0.9553927183151245</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114547371864319</v>
+        <v>0.9118788242340088</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582150936126709</v>
+        <v>0.85825514793396</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619678735733032</v>
+        <v>0.661193311214447</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020171165466309</v>
+        <v>0.9019849300384521</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002024809124862332</v>
       </c>
       <c r="C3" t="n">
-        <v>480</v>
+        <v>64</v>
       </c>
       <c r="D3" t="n">
-        <v>33250103</v>
+        <v>4159049</v>
       </c>
       <c r="E3" t="n">
-        <v>6550371</v>
+        <v>789584</v>
       </c>
       <c r="F3" t="n">
-        <v>282300</v>
+        <v>33547</v>
       </c>
       <c r="G3" t="n">
-        <v>31187</v>
+        <v>3690</v>
       </c>
       <c r="H3" t="n">
-        <v>24428</v>
+        <v>2639</v>
       </c>
       <c r="I3" t="n">
-        <v>1104</v>
+        <v>111</v>
       </c>
       <c r="J3" t="n">
-        <v>80129001</v>
+        <v>10016303</v>
       </c>
       <c r="K3" t="n">
-        <v>77264140</v>
+        <v>9639512</v>
       </c>
       <c r="L3" t="n">
-        <v>93631673</v>
+        <v>11707392</v>
       </c>
       <c r="M3" t="n">
-        <v>119741659</v>
+        <v>14967159</v>
       </c>
       <c r="N3" t="n">
-        <v>128849188</v>
+        <v>16106828</v>
       </c>
       <c r="O3" t="n">
-        <v>124519751</v>
+        <v>15569782</v>
       </c>
       <c r="P3" t="n">
-        <v>129058528</v>
+        <v>16132639</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8283538818359375</v>
+        <v>0.8336966037750244</v>
       </c>
       <c r="S3" t="n">
-        <v>0.476811558008194</v>
+        <v>0.4699350297451019</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3092633187770844</v>
+        <v>0.3100048899650574</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07142966985702515</v>
+        <v>0.07184947282075882</v>
       </c>
       <c r="V3" t="n">
-        <v>0.339497298002243</v>
+        <v>0.3342617750167847</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0165539626032114</v>
+        <v>0.01419494766741991</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38435590</v>
+        <v>4776143</v>
       </c>
       <c r="Z3" t="n">
-        <v>1581425</v>
+        <v>197221</v>
       </c>
       <c r="AA3" t="n">
-        <v>68001</v>
+        <v>8441</v>
       </c>
       <c r="AB3" t="n">
-        <v>54459</v>
+        <v>6838</v>
       </c>
       <c r="AC3" t="n">
-        <v>258</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80132976</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>88737218</v>
+        <v>11117918</v>
       </c>
       <c r="AG3" t="n">
-        <v>102138438</v>
+        <v>12743989</v>
       </c>
       <c r="AH3" t="n">
-        <v>122107746</v>
+        <v>15258909</v>
       </c>
       <c r="AI3" t="n">
-        <v>129681597</v>
+        <v>16209685</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126160401</v>
+        <v>15768676</v>
       </c>
       <c r="AK3" t="n">
-        <v>128983636</v>
+        <v>16122748</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575390219688416</v>
+        <v>0.9573953747749329</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9098982810974121</v>
+        <v>0.909557044506073</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573940396308899</v>
+        <v>0.8569823503494263</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613346934318542</v>
+        <v>0.6601602435112</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014958739280701</v>
+        <v>0.9011887311935425</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312471747398376</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.0319507024117701</v>
       </c>
       <c r="C4" t="n">
-        <v>215</v>
+        <v>38</v>
       </c>
       <c r="D4" t="n">
-        <v>11749951</v>
+        <v>1509850</v>
       </c>
       <c r="E4" t="n">
-        <v>12484769</v>
+        <v>1548864</v>
       </c>
       <c r="F4" t="n">
-        <v>1518823</v>
+        <v>185706</v>
       </c>
       <c r="G4" t="n">
-        <v>171628</v>
+        <v>20862</v>
       </c>
       <c r="H4" t="n">
-        <v>254165</v>
+        <v>30139</v>
       </c>
       <c r="I4" t="n">
-        <v>4313</v>
+        <v>452</v>
       </c>
       <c r="J4" t="n">
-        <v>3975</v>
+        <v>319</v>
       </c>
       <c r="K4" t="n">
-        <v>13232687</v>
+        <v>1701404</v>
       </c>
       <c r="L4" t="n">
-        <v>10821263</v>
+        <v>1326297</v>
       </c>
       <c r="M4" t="n">
-        <v>3424323</v>
+        <v>424501</v>
       </c>
       <c r="N4" t="n">
-        <v>1073553</v>
+        <v>133168</v>
       </c>
       <c r="O4" t="n">
-        <v>2039909</v>
+        <v>248925</v>
       </c>
       <c r="P4" t="n">
-        <v>31150</v>
+        <v>3371</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999606609344482</v>
+        <v>0.9999747276306152</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7676989436149597</v>
+        <v>0.7667059302330017</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5045380592346191</v>
+        <v>0.5019756555557251</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3499200046062469</v>
+        <v>0.3517599403858185</v>
       </c>
       <c r="U4" t="n">
-        <v>0.055481918156147</v>
+        <v>0.05617555975914001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3690537512302399</v>
+        <v>0.3670187890529633</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03193624317646027</v>
+        <v>0.02752004191279411</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1643061</v>
+        <v>208344</v>
       </c>
       <c r="Z4" t="n">
-        <v>23824653</v>
+        <v>2997819</v>
       </c>
       <c r="AA4" t="n">
-        <v>662423</v>
+        <v>82986</v>
       </c>
       <c r="AB4" t="n">
-        <v>44064</v>
+        <v>5563</v>
       </c>
       <c r="AC4" t="n">
-        <v>9119</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1759609</v>
+        <v>222998</v>
       </c>
       <c r="AG4" t="n">
-        <v>2314498</v>
+        <v>289700</v>
       </c>
       <c r="AH4" t="n">
-        <v>1058236</v>
+        <v>132751</v>
       </c>
       <c r="AI4" t="n">
-        <v>241144</v>
+        <v>30311</v>
       </c>
       <c r="AJ4" t="n">
-        <v>399259</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106042</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9568807482719421</v>
+        <v>0.9563930034637451</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106758832931519</v>
+        <v>0.9107164144515991</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578044176101685</v>
+        <v>0.8576182723045349</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6616511344909668</v>
+        <v>0.6606763601303101</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017564058303833</v>
+        <v>0.901586651802063</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313456416130066</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>522</v>
+        <v>46</v>
       </c>
       <c r="D5" t="n">
-        <v>1097197</v>
+        <v>141839</v>
       </c>
       <c r="E5" t="n">
-        <v>3158458</v>
+        <v>395170</v>
       </c>
       <c r="F5" t="n">
-        <v>2310450</v>
+        <v>290766</v>
       </c>
       <c r="G5" t="n">
-        <v>278573</v>
+        <v>34757</v>
       </c>
       <c r="H5" t="n">
-        <v>618030</v>
+        <v>74522</v>
       </c>
       <c r="I5" t="n">
-        <v>7588</v>
+        <v>840</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6889870</v>
+        <v>829635</v>
       </c>
       <c r="L5" t="n">
-        <v>13699095</v>
+        <v>1747047</v>
       </c>
       <c r="M5" t="n">
-        <v>5160368</v>
+        <v>647174</v>
       </c>
       <c r="N5" t="n">
-        <v>663054</v>
+        <v>83166</v>
       </c>
       <c r="O5" t="n">
-        <v>2692962</v>
+        <v>340121</v>
       </c>
       <c r="P5" t="n">
-        <v>1521511</v>
+        <v>190842</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999696016311646</v>
+        <v>0.9999804496765137</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8459656238555908</v>
+        <v>0.8450030088424683</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8123012781143188</v>
+        <v>0.8117930889129639</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9342858195304871</v>
+        <v>0.9343722462654114</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9867066144943237</v>
+        <v>0.9867520332336426</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9637707471847534</v>
+        <v>0.963927686214447</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9881146550178528</v>
+        <v>0.9881066679954529</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>64236</v>
+        <v>8050</v>
       </c>
       <c r="Z5" t="n">
-        <v>683114</v>
+        <v>86223</v>
       </c>
       <c r="AA5" t="n">
-        <v>6405435</v>
+        <v>803798</v>
       </c>
       <c r="AB5" t="n">
-        <v>79701</v>
+        <v>9997</v>
       </c>
       <c r="AC5" t="n">
-        <v>233268</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1704383</v>
+        <v>212541</v>
       </c>
       <c r="AG5" t="n">
-        <v>2359211</v>
+        <v>298092</v>
       </c>
       <c r="AH5" t="n">
-        <v>1065383</v>
+        <v>134142</v>
       </c>
       <c r="AI5" t="n">
-        <v>241827</v>
+        <v>30451</v>
       </c>
       <c r="AJ5" t="n">
-        <v>401615</v>
+        <v>50482</v>
       </c>
       <c r="AK5" t="n">
-        <v>106369</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734838008880615</v>
+        <v>0.9733282327651978</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642236232757568</v>
+        <v>0.9640045166015625</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837440848350525</v>
+        <v>0.9836558699607849</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963029623031616</v>
+        <v>0.9962790012359619</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938694834709167</v>
+        <v>0.993844747543335</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983740448951721</v>
+        <v>0.9983706474304199</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>319</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>196253</v>
+        <v>25474</v>
       </c>
       <c r="E6" t="n">
-        <v>208090</v>
+        <v>25935</v>
       </c>
       <c r="F6" t="n">
-        <v>191563</v>
+        <v>23745</v>
       </c>
       <c r="G6" t="n">
-        <v>51005</v>
+        <v>6438</v>
       </c>
       <c r="H6" t="n">
-        <v>65049</v>
+        <v>7807</v>
       </c>
       <c r="I6" t="n">
-        <v>1780</v>
+        <v>179</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>51905</v>
+        <v>6568</v>
       </c>
       <c r="Z6" t="n">
-        <v>42831</v>
+        <v>5365</v>
       </c>
       <c r="AA6" t="n">
-        <v>87352</v>
+        <v>11023</v>
       </c>
       <c r="AB6" t="n">
-        <v>472232</v>
+        <v>59153</v>
       </c>
       <c r="AC6" t="n">
-        <v>55891</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1106</v>
+        <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>172835</v>
+        <v>22070</v>
       </c>
       <c r="E7" t="n">
-        <v>803403</v>
+        <v>102420</v>
       </c>
       <c r="F7" t="n">
-        <v>1222738</v>
+        <v>154815</v>
       </c>
       <c r="G7" t="n">
-        <v>476515</v>
+        <v>58963</v>
       </c>
       <c r="H7" t="n">
-        <v>1384178</v>
+        <v>170772</v>
       </c>
       <c r="I7" t="n">
-        <v>16365</v>
+        <v>1789</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>183</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>6480</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>237812</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60794</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3675525</v>
+        <v>460411</v>
       </c>
       <c r="AD7" t="n">
-        <v>96346</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1333</v>
+        <v>81</v>
       </c>
       <c r="D8" t="n">
-        <v>16451</v>
+        <v>2171</v>
       </c>
       <c r="E8" t="n">
-        <v>100941</v>
+        <v>13188</v>
       </c>
       <c r="F8" t="n">
-        <v>208899</v>
+        <v>26688</v>
       </c>
       <c r="G8" t="n">
-        <v>115650</v>
+        <v>14896</v>
       </c>
       <c r="H8" t="n">
-        <v>1078237</v>
+        <v>133818</v>
       </c>
       <c r="I8" t="n">
-        <v>25611</v>
+        <v>2748</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2648</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2126</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100723</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
